--- a/b1_urls.xlsx
+++ b/b1_urls.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="553">
   <si>
     <t>x</t>
   </si>
@@ -680,6 +680,171 @@
     <t>221</t>
   </si>
   <si>
+    <t>222</t>
+  </si>
+  <si>
+    <t>223</t>
+  </si>
+  <si>
+    <t>224</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
+    <t>226</t>
+  </si>
+  <si>
+    <t>227</t>
+  </si>
+  <si>
+    <t>228</t>
+  </si>
+  <si>
+    <t>229</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>232</t>
+  </si>
+  <si>
+    <t>233</t>
+  </si>
+  <si>
+    <t>234</t>
+  </si>
+  <si>
+    <t>235</t>
+  </si>
+  <si>
+    <t>236</t>
+  </si>
+  <si>
+    <t>237</t>
+  </si>
+  <si>
+    <t>238</t>
+  </si>
+  <si>
+    <t>239</t>
+  </si>
+  <si>
+    <t>240</t>
+  </si>
+  <si>
+    <t>241</t>
+  </si>
+  <si>
+    <t>242</t>
+  </si>
+  <si>
+    <t>243</t>
+  </si>
+  <si>
+    <t>244</t>
+  </si>
+  <si>
+    <t>245</t>
+  </si>
+  <si>
+    <t>246</t>
+  </si>
+  <si>
+    <t>247</t>
+  </si>
+  <si>
+    <t>248</t>
+  </si>
+  <si>
+    <t>249</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>251</t>
+  </si>
+  <si>
+    <t>252</t>
+  </si>
+  <si>
+    <t>253</t>
+  </si>
+  <si>
+    <t>254</t>
+  </si>
+  <si>
+    <t>255</t>
+  </si>
+  <si>
+    <t>256</t>
+  </si>
+  <si>
+    <t>257</t>
+  </si>
+  <si>
+    <t>258</t>
+  </si>
+  <si>
+    <t>259</t>
+  </si>
+  <si>
+    <t>260</t>
+  </si>
+  <si>
+    <t>261</t>
+  </si>
+  <si>
+    <t>262</t>
+  </si>
+  <si>
+    <t>263</t>
+  </si>
+  <si>
+    <t>264</t>
+  </si>
+  <si>
+    <t>265</t>
+  </si>
+  <si>
+    <t>266</t>
+  </si>
+  <si>
+    <t>267</t>
+  </si>
+  <si>
+    <t>268</t>
+  </si>
+  <si>
+    <t>269</t>
+  </si>
+  <si>
+    <t>270</t>
+  </si>
+  <si>
+    <t>271</t>
+  </si>
+  <si>
+    <t>272</t>
+  </si>
+  <si>
+    <t>273</t>
+  </si>
+  <si>
+    <t>274</t>
+  </si>
+  <si>
+    <t>275</t>
+  </si>
+  <si>
+    <t>276</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/059136bc/Club-Brugge-Mechelen-July-26-2024-Belgian-Pro-League</t>
   </si>
   <si>
@@ -1052,12 +1217,12 @@
     <t>https://fbref.com/en/matches/847465bd/Sint-Truiden-Genk-December-1-2024-Belgian-Pro-League</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/f9e7c99b/OH-Leuven-Anderlecht-December-1-2024-Belgian-Pro-League</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/4285d88e/Beerschot-Wilrijk-Cercle-Brugge-December-1-2024-Belgian-Pro-League</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/f9e7c99b/OH-Leuven-Anderlecht-December-1-2024-Belgian-Pro-League</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/646bb22c/Union-SG-Antwerp-December-1-2024-Belgian-Pro-League</t>
   </si>
   <si>
@@ -1154,12 +1319,12 @@
     <t>https://fbref.com/en/matches/0c9e22f9/OH-Leuven-Beerschot-Wilrijk-December-27-2024-Belgian-Pro-League</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/f5c8e1ed/Sint-Truiden-Cercle-Brugge-December-27-2024-Belgian-Pro-League</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/1fa133d4/Anderlecht-Dender-December-27-2024-Belgian-Pro-League</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/f5c8e1ed/Sint-Truiden-Cercle-Brugge-December-27-2024-Belgian-Pro-League</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/3b86978a/Standard-Liege-Kortrijk-January-10-2025-Belgian-Pro-League</t>
   </si>
   <si>
@@ -1331,16 +1496,181 @@
     <t>https://fbref.com/en/matches/8a6a7bc5/Charleroi-Genk-February-28-2025-Belgian-Pro-League</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/f5176ab6/Gent-Club-Brugge-March-1-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/13d0a243/Cercle-Brugge-Antwerp-March-1-2025-Belgian-Pro-League</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/f5176ab6/Gent-Club-Brugge-March-1-2025-Belgian-Pro-League</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/dbab2454/Sint-Truiden-Kortrijk-March-1-2025-Belgian-Pro-League</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/e5be2cb3/Union-SG-Dender-March-1-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/30821f78/Beerschot-Wilrijk-Mechelen-March-2-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/31ec57a6/Standard-Liege-Anderlecht-March-2-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/dd474c73/OH-Leuven-Westerlo-March-2-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f7f11536/Sint-Truiden-Beerschot-Wilrijk-March-7-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c6ba9776/Kortrijk-OH-Leuven-March-8-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/0704491c/Charleroi-Mechelen-March-8-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/fa488445/Dender-Genk-March-8-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ac608178/Cercle-Brugge-Club-Brugge-March-9-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f6f2d775/Westerlo-Anderlecht-March-9-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/765696ed/Antwerp-Gent-March-9-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/0b63c560/Union-SG-Standard-Liege-March-9-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8de170db/Genk-Union-SG-March-15-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a39e4d18/Standard-Liege-Antwerp-March-16-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/3aa7907d/Beerschot-Wilrijk-Westerlo-March-16-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f1a378be/Mechelen-Dender-March-16-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/02aec0c9/Gent-Kortrijk-March-16-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8ea772b0/Club-Brugge-Charleroi-March-16-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ce003b8c/Anderlecht-Cercle-Brugge-March-16-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/4191f845/OH-Leuven-Sint-Truiden-March-16-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ddc2b85a/OH-Leuven-Charleroi-March-28-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/77913b22/Beerschot-Wilrijk-Sint-Truiden-March-29-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9f7c914c/Standard-Liege-Mechelen-March-29-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b6b5c3c6/Union-SG-Antwerp-March-29-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/83dafb7b/Club-Brugge-Anderlecht-March-30-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/32b55843/Kortrijk-Cercle-Brugge-March-30-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ed6d62dd/Genk-Gent-March-30-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/dae83c25/Dender-Westerlo-March-30-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/0146ff9b/Mechelen-Dender-April-4-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/2661752f/Cercle-Brugge-Beerschot-Wilrijk-April-5-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/05f17576/Westerlo-OH-Leuven-April-5-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/5a9becb2/Gent-Union-SG-April-5-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/cf865a64/Antwerp-Club-Brugge-April-6-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/724be093/Sint-Truiden-Kortrijk-April-6-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/976e92ac/Anderlecht-Genk-April-6-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ac7613c0/Charleroi-Standard-Liege-April-6-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/0aec4d7a/Westerlo-Charleroi-April-11-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a7eb54d6/Kortrijk-Beerschot-Wilrijk-April-12-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/0b8eaf5c/Sint-Truiden-Cercle-Brugge-April-12-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/060e4b24/Union-SG-Anderlecht-April-12-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c1535d8d/Antwerp-Gent-April-13-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f3f79a9a/Mechelen-OH-Leuven-April-13-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ad1000d4/Club-Brugge-Genk-April-13-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/914a0b24/Dender-Standard-Liege-April-13-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/4a9366e1/OH-Leuven-Dender-April-19-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ace69fda/Charleroi-Mechelen-April-19-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a90bff81/Standard-Liege-Westerlo-April-19-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/481b5403/Anderlecht-Antwerp-April-20-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ae64483f/Genk-Union-SG-April-20-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/dbfd1536/Gent-Club-Brugge-April-20-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8804f4b3/Standard-Liege-OH-Leuven-April-22-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/73312bdd/Dender-Charleroi-April-22-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/05b8de63/Mechelen-Westerlo-April-22-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f9896c57/Antwerp-Genk-April-23-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/1dfabcca/Anderlecht-Gent-April-23-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/2dae3b35/Club-Brugge-Union-SG-April-24-2025-Belgian-Pro-League</t>
   </si>
 </sst>
 </file>
@@ -1399,7 +1729,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>222</v>
+        <v>277</v>
       </c>
     </row>
     <row r="3">
@@ -1407,7 +1737,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>223</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4">
@@ -1415,7 +1745,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>224</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5">
@@ -1423,7 +1753,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>225</v>
+        <v>280</v>
       </c>
     </row>
     <row r="6">
@@ -1431,7 +1761,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>226</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7">
@@ -1439,7 +1769,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>227</v>
+        <v>282</v>
       </c>
     </row>
     <row r="8">
@@ -1447,7 +1777,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>228</v>
+        <v>283</v>
       </c>
     </row>
     <row r="9">
@@ -1455,7 +1785,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>229</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -1463,7 +1793,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>230</v>
+        <v>285</v>
       </c>
     </row>
     <row r="11">
@@ -1471,7 +1801,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>231</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -1479,7 +1809,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>232</v>
+        <v>287</v>
       </c>
     </row>
     <row r="13">
@@ -1487,7 +1817,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>233</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14">
@@ -1495,7 +1825,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>234</v>
+        <v>289</v>
       </c>
     </row>
     <row r="15">
@@ -1503,7 +1833,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>235</v>
+        <v>290</v>
       </c>
     </row>
     <row r="16">
@@ -1511,7 +1841,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>236</v>
+        <v>291</v>
       </c>
     </row>
     <row r="17">
@@ -1519,7 +1849,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>237</v>
+        <v>292</v>
       </c>
     </row>
     <row r="18">
@@ -1527,7 +1857,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>238</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19">
@@ -1535,7 +1865,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>239</v>
+        <v>294</v>
       </c>
     </row>
     <row r="20">
@@ -1543,7 +1873,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>240</v>
+        <v>295</v>
       </c>
     </row>
     <row r="21">
@@ -1551,7 +1881,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>241</v>
+        <v>296</v>
       </c>
     </row>
     <row r="22">
@@ -1559,7 +1889,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>242</v>
+        <v>297</v>
       </c>
     </row>
     <row r="23">
@@ -1567,7 +1897,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>243</v>
+        <v>298</v>
       </c>
     </row>
     <row r="24">
@@ -1575,7 +1905,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>244</v>
+        <v>299</v>
       </c>
     </row>
     <row r="25">
@@ -1583,7 +1913,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>245</v>
+        <v>300</v>
       </c>
     </row>
     <row r="26">
@@ -1591,7 +1921,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>246</v>
+        <v>301</v>
       </c>
     </row>
     <row r="27">
@@ -1599,7 +1929,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>247</v>
+        <v>302</v>
       </c>
     </row>
     <row r="28">
@@ -1607,7 +1937,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>248</v>
+        <v>303</v>
       </c>
     </row>
     <row r="29">
@@ -1615,7 +1945,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>249</v>
+        <v>304</v>
       </c>
     </row>
     <row r="30">
@@ -1623,7 +1953,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>250</v>
+        <v>305</v>
       </c>
     </row>
     <row r="31">
@@ -1631,7 +1961,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>251</v>
+        <v>306</v>
       </c>
     </row>
     <row r="32">
@@ -1639,7 +1969,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>252</v>
+        <v>307</v>
       </c>
     </row>
     <row r="33">
@@ -1647,7 +1977,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>253</v>
+        <v>308</v>
       </c>
     </row>
     <row r="34">
@@ -1655,7 +1985,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>254</v>
+        <v>309</v>
       </c>
     </row>
     <row r="35">
@@ -1663,7 +1993,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>255</v>
+        <v>310</v>
       </c>
     </row>
     <row r="36">
@@ -1671,7 +2001,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>256</v>
+        <v>311</v>
       </c>
     </row>
     <row r="37">
@@ -1679,7 +2009,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>257</v>
+        <v>312</v>
       </c>
     </row>
     <row r="38">
@@ -1687,7 +2017,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>258</v>
+        <v>313</v>
       </c>
     </row>
     <row r="39">
@@ -1695,7 +2025,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>259</v>
+        <v>314</v>
       </c>
     </row>
     <row r="40">
@@ -1703,7 +2033,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>260</v>
+        <v>315</v>
       </c>
     </row>
     <row r="41">
@@ -1711,7 +2041,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>261</v>
+        <v>316</v>
       </c>
     </row>
     <row r="42">
@@ -1719,7 +2049,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>262</v>
+        <v>317</v>
       </c>
     </row>
     <row r="43">
@@ -1727,7 +2057,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>263</v>
+        <v>318</v>
       </c>
     </row>
     <row r="44">
@@ -1735,7 +2065,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>264</v>
+        <v>319</v>
       </c>
     </row>
     <row r="45">
@@ -1743,7 +2073,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>265</v>
+        <v>320</v>
       </c>
     </row>
     <row r="46">
@@ -1751,7 +2081,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>266</v>
+        <v>321</v>
       </c>
     </row>
     <row r="47">
@@ -1759,7 +2089,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>267</v>
+        <v>322</v>
       </c>
     </row>
     <row r="48">
@@ -1767,7 +2097,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>268</v>
+        <v>323</v>
       </c>
     </row>
     <row r="49">
@@ -1775,7 +2105,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>269</v>
+        <v>324</v>
       </c>
     </row>
     <row r="50">
@@ -1783,7 +2113,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>270</v>
+        <v>325</v>
       </c>
     </row>
     <row r="51">
@@ -1791,7 +2121,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>271</v>
+        <v>326</v>
       </c>
     </row>
     <row r="52">
@@ -1799,7 +2129,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>272</v>
+        <v>327</v>
       </c>
     </row>
     <row r="53">
@@ -1807,7 +2137,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>273</v>
+        <v>328</v>
       </c>
     </row>
     <row r="54">
@@ -1815,7 +2145,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>274</v>
+        <v>329</v>
       </c>
     </row>
     <row r="55">
@@ -1823,7 +2153,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>275</v>
+        <v>330</v>
       </c>
     </row>
     <row r="56">
@@ -1831,7 +2161,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>276</v>
+        <v>331</v>
       </c>
     </row>
     <row r="57">
@@ -1839,7 +2169,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>277</v>
+        <v>332</v>
       </c>
     </row>
     <row r="58">
@@ -1847,7 +2177,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>278</v>
+        <v>333</v>
       </c>
     </row>
     <row r="59">
@@ -1855,7 +2185,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>279</v>
+        <v>334</v>
       </c>
     </row>
     <row r="60">
@@ -1863,7 +2193,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>280</v>
+        <v>335</v>
       </c>
     </row>
     <row r="61">
@@ -1871,7 +2201,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
     </row>
     <row r="62">
@@ -1879,7 +2209,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>282</v>
+        <v>337</v>
       </c>
     </row>
     <row r="63">
@@ -1887,7 +2217,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>283</v>
+        <v>338</v>
       </c>
     </row>
     <row r="64">
@@ -1895,7 +2225,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>284</v>
+        <v>339</v>
       </c>
     </row>
     <row r="65">
@@ -1903,7 +2233,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>285</v>
+        <v>340</v>
       </c>
     </row>
     <row r="66">
@@ -1911,7 +2241,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>286</v>
+        <v>341</v>
       </c>
     </row>
     <row r="67">
@@ -1919,7 +2249,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>287</v>
+        <v>342</v>
       </c>
     </row>
     <row r="68">
@@ -1927,7 +2257,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>288</v>
+        <v>343</v>
       </c>
     </row>
     <row r="69">
@@ -1935,7 +2265,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>289</v>
+        <v>344</v>
       </c>
     </row>
     <row r="70">
@@ -1943,7 +2273,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>290</v>
+        <v>345</v>
       </c>
     </row>
     <row r="71">
@@ -1951,7 +2281,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>291</v>
+        <v>346</v>
       </c>
     </row>
     <row r="72">
@@ -1959,7 +2289,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>292</v>
+        <v>347</v>
       </c>
     </row>
     <row r="73">
@@ -1967,7 +2297,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>293</v>
+        <v>348</v>
       </c>
     </row>
     <row r="74">
@@ -1975,7 +2305,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>294</v>
+        <v>349</v>
       </c>
     </row>
     <row r="75">
@@ -1983,7 +2313,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>295</v>
+        <v>350</v>
       </c>
     </row>
     <row r="76">
@@ -1991,7 +2321,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>296</v>
+        <v>351</v>
       </c>
     </row>
     <row r="77">
@@ -1999,7 +2329,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>297</v>
+        <v>352</v>
       </c>
     </row>
     <row r="78">
@@ -2007,7 +2337,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>298</v>
+        <v>353</v>
       </c>
     </row>
     <row r="79">
@@ -2015,7 +2345,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>299</v>
+        <v>354</v>
       </c>
     </row>
     <row r="80">
@@ -2023,7 +2353,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>300</v>
+        <v>355</v>
       </c>
     </row>
     <row r="81">
@@ -2031,7 +2361,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>301</v>
+        <v>356</v>
       </c>
     </row>
     <row r="82">
@@ -2039,7 +2369,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>302</v>
+        <v>357</v>
       </c>
     </row>
     <row r="83">
@@ -2047,7 +2377,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>303</v>
+        <v>358</v>
       </c>
     </row>
     <row r="84">
@@ -2055,7 +2385,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>304</v>
+        <v>359</v>
       </c>
     </row>
     <row r="85">
@@ -2063,7 +2393,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>305</v>
+        <v>360</v>
       </c>
     </row>
     <row r="86">
@@ -2071,7 +2401,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>306</v>
+        <v>361</v>
       </c>
     </row>
     <row r="87">
@@ -2079,7 +2409,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>307</v>
+        <v>362</v>
       </c>
     </row>
     <row r="88">
@@ -2087,7 +2417,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>308</v>
+        <v>363</v>
       </c>
     </row>
     <row r="89">
@@ -2095,7 +2425,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>309</v>
+        <v>364</v>
       </c>
     </row>
     <row r="90">
@@ -2103,7 +2433,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>310</v>
+        <v>365</v>
       </c>
     </row>
     <row r="91">
@@ -2111,7 +2441,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>311</v>
+        <v>366</v>
       </c>
     </row>
     <row r="92">
@@ -2119,7 +2449,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>312</v>
+        <v>367</v>
       </c>
     </row>
     <row r="93">
@@ -2127,7 +2457,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>313</v>
+        <v>368</v>
       </c>
     </row>
     <row r="94">
@@ -2135,7 +2465,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>314</v>
+        <v>369</v>
       </c>
     </row>
     <row r="95">
@@ -2143,7 +2473,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>315</v>
+        <v>370</v>
       </c>
     </row>
     <row r="96">
@@ -2151,7 +2481,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>316</v>
+        <v>371</v>
       </c>
     </row>
     <row r="97">
@@ -2159,7 +2489,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>317</v>
+        <v>372</v>
       </c>
     </row>
     <row r="98">
@@ -2167,7 +2497,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>318</v>
+        <v>373</v>
       </c>
     </row>
     <row r="99">
@@ -2175,7 +2505,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>319</v>
+        <v>374</v>
       </c>
     </row>
     <row r="100">
@@ -2183,7 +2513,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>320</v>
+        <v>375</v>
       </c>
     </row>
     <row r="101">
@@ -2191,7 +2521,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>321</v>
+        <v>376</v>
       </c>
     </row>
     <row r="102">
@@ -2199,7 +2529,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>322</v>
+        <v>377</v>
       </c>
     </row>
     <row r="103">
@@ -2207,7 +2537,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>323</v>
+        <v>378</v>
       </c>
     </row>
     <row r="104">
@@ -2215,7 +2545,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>324</v>
+        <v>379</v>
       </c>
     </row>
     <row r="105">
@@ -2223,7 +2553,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>325</v>
+        <v>380</v>
       </c>
     </row>
     <row r="106">
@@ -2231,7 +2561,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>326</v>
+        <v>381</v>
       </c>
     </row>
     <row r="107">
@@ -2239,7 +2569,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>327</v>
+        <v>382</v>
       </c>
     </row>
     <row r="108">
@@ -2247,7 +2577,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>328</v>
+        <v>383</v>
       </c>
     </row>
     <row r="109">
@@ -2255,7 +2585,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>329</v>
+        <v>384</v>
       </c>
     </row>
     <row r="110">
@@ -2263,7 +2593,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>330</v>
+        <v>385</v>
       </c>
     </row>
     <row r="111">
@@ -2271,7 +2601,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>331</v>
+        <v>386</v>
       </c>
     </row>
     <row r="112">
@@ -2279,7 +2609,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>332</v>
+        <v>387</v>
       </c>
     </row>
     <row r="113">
@@ -2287,7 +2617,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>333</v>
+        <v>388</v>
       </c>
     </row>
     <row r="114">
@@ -2295,7 +2625,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>334</v>
+        <v>389</v>
       </c>
     </row>
     <row r="115">
@@ -2303,7 +2633,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>335</v>
+        <v>390</v>
       </c>
     </row>
     <row r="116">
@@ -2311,7 +2641,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>336</v>
+        <v>391</v>
       </c>
     </row>
     <row r="117">
@@ -2319,7 +2649,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>337</v>
+        <v>392</v>
       </c>
     </row>
     <row r="118">
@@ -2327,7 +2657,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>338</v>
+        <v>393</v>
       </c>
     </row>
     <row r="119">
@@ -2335,7 +2665,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>339</v>
+        <v>394</v>
       </c>
     </row>
     <row r="120">
@@ -2343,7 +2673,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>340</v>
+        <v>395</v>
       </c>
     </row>
     <row r="121">
@@ -2351,7 +2681,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>341</v>
+        <v>396</v>
       </c>
     </row>
     <row r="122">
@@ -2359,7 +2689,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>342</v>
+        <v>397</v>
       </c>
     </row>
     <row r="123">
@@ -2367,7 +2697,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>343</v>
+        <v>398</v>
       </c>
     </row>
     <row r="124">
@@ -2375,7 +2705,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>344</v>
+        <v>399</v>
       </c>
     </row>
     <row r="125">
@@ -2383,7 +2713,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>345</v>
+        <v>400</v>
       </c>
     </row>
     <row r="126">
@@ -2391,7 +2721,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>346</v>
+        <v>401</v>
       </c>
     </row>
     <row r="127">
@@ -2399,7 +2729,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>347</v>
+        <v>402</v>
       </c>
     </row>
     <row r="128">
@@ -2407,7 +2737,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>348</v>
+        <v>403</v>
       </c>
     </row>
     <row r="129">
@@ -2415,7 +2745,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>349</v>
+        <v>404</v>
       </c>
     </row>
     <row r="130">
@@ -2423,7 +2753,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>350</v>
+        <v>405</v>
       </c>
     </row>
     <row r="131">
@@ -2431,7 +2761,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>351</v>
+        <v>406</v>
       </c>
     </row>
     <row r="132">
@@ -2439,7 +2769,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>352</v>
+        <v>407</v>
       </c>
     </row>
     <row r="133">
@@ -2447,7 +2777,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>353</v>
+        <v>408</v>
       </c>
     </row>
     <row r="134">
@@ -2455,7 +2785,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>354</v>
+        <v>409</v>
       </c>
     </row>
     <row r="135">
@@ -2463,7 +2793,7 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>355</v>
+        <v>410</v>
       </c>
     </row>
     <row r="136">
@@ -2471,7 +2801,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>356</v>
+        <v>411</v>
       </c>
     </row>
     <row r="137">
@@ -2479,7 +2809,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>357</v>
+        <v>412</v>
       </c>
     </row>
     <row r="138">
@@ -2487,7 +2817,7 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>358</v>
+        <v>413</v>
       </c>
     </row>
     <row r="139">
@@ -2495,7 +2825,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>359</v>
+        <v>414</v>
       </c>
     </row>
     <row r="140">
@@ -2503,7 +2833,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>360</v>
+        <v>415</v>
       </c>
     </row>
     <row r="141">
@@ -2511,7 +2841,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>361</v>
+        <v>416</v>
       </c>
     </row>
     <row r="142">
@@ -2519,7 +2849,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>362</v>
+        <v>417</v>
       </c>
     </row>
     <row r="143">
@@ -2527,7 +2857,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>363</v>
+        <v>418</v>
       </c>
     </row>
     <row r="144">
@@ -2535,7 +2865,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>364</v>
+        <v>419</v>
       </c>
     </row>
     <row r="145">
@@ -2543,7 +2873,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>365</v>
+        <v>420</v>
       </c>
     </row>
     <row r="146">
@@ -2551,7 +2881,7 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>366</v>
+        <v>421</v>
       </c>
     </row>
     <row r="147">
@@ -2559,7 +2889,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>367</v>
+        <v>422</v>
       </c>
     </row>
     <row r="148">
@@ -2567,7 +2897,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>368</v>
+        <v>423</v>
       </c>
     </row>
     <row r="149">
@@ -2575,7 +2905,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>369</v>
+        <v>424</v>
       </c>
     </row>
     <row r="150">
@@ -2583,7 +2913,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>370</v>
+        <v>425</v>
       </c>
     </row>
     <row r="151">
@@ -2591,7 +2921,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>371</v>
+        <v>426</v>
       </c>
     </row>
     <row r="152">
@@ -2599,7 +2929,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>372</v>
+        <v>427</v>
       </c>
     </row>
     <row r="153">
@@ -2607,7 +2937,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>373</v>
+        <v>428</v>
       </c>
     </row>
     <row r="154">
@@ -2615,7 +2945,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>374</v>
+        <v>429</v>
       </c>
     </row>
     <row r="155">
@@ -2623,7 +2953,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>375</v>
+        <v>430</v>
       </c>
     </row>
     <row r="156">
@@ -2631,7 +2961,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>376</v>
+        <v>431</v>
       </c>
     </row>
     <row r="157">
@@ -2639,7 +2969,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>377</v>
+        <v>432</v>
       </c>
     </row>
     <row r="158">
@@ -2647,7 +2977,7 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>378</v>
+        <v>433</v>
       </c>
     </row>
     <row r="159">
@@ -2655,7 +2985,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>379</v>
+        <v>434</v>
       </c>
     </row>
     <row r="160">
@@ -2663,7 +2993,7 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>380</v>
+        <v>435</v>
       </c>
     </row>
     <row r="161">
@@ -2671,7 +3001,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>381</v>
+        <v>436</v>
       </c>
     </row>
     <row r="162">
@@ -2679,7 +3009,7 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>382</v>
+        <v>437</v>
       </c>
     </row>
     <row r="163">
@@ -2687,7 +3017,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>383</v>
+        <v>438</v>
       </c>
     </row>
     <row r="164">
@@ -2695,7 +3025,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>384</v>
+        <v>439</v>
       </c>
     </row>
     <row r="165">
@@ -2703,7 +3033,7 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>385</v>
+        <v>440</v>
       </c>
     </row>
     <row r="166">
@@ -2711,7 +3041,7 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>386</v>
+        <v>441</v>
       </c>
     </row>
     <row r="167">
@@ -2719,7 +3049,7 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>387</v>
+        <v>442</v>
       </c>
     </row>
     <row r="168">
@@ -2727,7 +3057,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>388</v>
+        <v>443</v>
       </c>
     </row>
     <row r="169">
@@ -2735,7 +3065,7 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>389</v>
+        <v>444</v>
       </c>
     </row>
     <row r="170">
@@ -2743,7 +3073,7 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>390</v>
+        <v>445</v>
       </c>
     </row>
     <row r="171">
@@ -2751,7 +3081,7 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>391</v>
+        <v>446</v>
       </c>
     </row>
     <row r="172">
@@ -2759,7 +3089,7 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>392</v>
+        <v>447</v>
       </c>
     </row>
     <row r="173">
@@ -2767,7 +3097,7 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>393</v>
+        <v>448</v>
       </c>
     </row>
     <row r="174">
@@ -2775,7 +3105,7 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>394</v>
+        <v>449</v>
       </c>
     </row>
     <row r="175">
@@ -2783,7 +3113,7 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>395</v>
+        <v>450</v>
       </c>
     </row>
     <row r="176">
@@ -2791,7 +3121,7 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>396</v>
+        <v>451</v>
       </c>
     </row>
     <row r="177">
@@ -2799,7 +3129,7 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>397</v>
+        <v>452</v>
       </c>
     </row>
     <row r="178">
@@ -2807,7 +3137,7 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>398</v>
+        <v>453</v>
       </c>
     </row>
     <row r="179">
@@ -2815,7 +3145,7 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>399</v>
+        <v>454</v>
       </c>
     </row>
     <row r="180">
@@ -2823,7 +3153,7 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>400</v>
+        <v>455</v>
       </c>
     </row>
     <row r="181">
@@ -2831,7 +3161,7 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>401</v>
+        <v>456</v>
       </c>
     </row>
     <row r="182">
@@ -2839,7 +3169,7 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>402</v>
+        <v>457</v>
       </c>
     </row>
     <row r="183">
@@ -2847,7 +3177,7 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>403</v>
+        <v>458</v>
       </c>
     </row>
     <row r="184">
@@ -2855,7 +3185,7 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>404</v>
+        <v>459</v>
       </c>
     </row>
     <row r="185">
@@ -2863,7 +3193,7 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>405</v>
+        <v>460</v>
       </c>
     </row>
     <row r="186">
@@ -2871,7 +3201,7 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>406</v>
+        <v>461</v>
       </c>
     </row>
     <row r="187">
@@ -2879,7 +3209,7 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>407</v>
+        <v>462</v>
       </c>
     </row>
     <row r="188">
@@ -2887,7 +3217,7 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>408</v>
+        <v>463</v>
       </c>
     </row>
     <row r="189">
@@ -2895,7 +3225,7 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>409</v>
+        <v>464</v>
       </c>
     </row>
     <row r="190">
@@ -2903,7 +3233,7 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>410</v>
+        <v>465</v>
       </c>
     </row>
     <row r="191">
@@ -2911,7 +3241,7 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>411</v>
+        <v>466</v>
       </c>
     </row>
     <row r="192">
@@ -2919,7 +3249,7 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>412</v>
+        <v>467</v>
       </c>
     </row>
     <row r="193">
@@ -2927,7 +3257,7 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>413</v>
+        <v>468</v>
       </c>
     </row>
     <row r="194">
@@ -2935,7 +3265,7 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>414</v>
+        <v>469</v>
       </c>
     </row>
     <row r="195">
@@ -2943,7 +3273,7 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
     </row>
     <row r="196">
@@ -2951,7 +3281,7 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>416</v>
+        <v>471</v>
       </c>
     </row>
     <row r="197">
@@ -2959,7 +3289,7 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>417</v>
+        <v>472</v>
       </c>
     </row>
     <row r="198">
@@ -2967,7 +3297,7 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>418</v>
+        <v>473</v>
       </c>
     </row>
     <row r="199">
@@ -2975,7 +3305,7 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>419</v>
+        <v>474</v>
       </c>
     </row>
     <row r="200">
@@ -2983,7 +3313,7 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>420</v>
+        <v>475</v>
       </c>
     </row>
     <row r="201">
@@ -2991,7 +3321,7 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>421</v>
+        <v>476</v>
       </c>
     </row>
     <row r="202">
@@ -2999,7 +3329,7 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>422</v>
+        <v>477</v>
       </c>
     </row>
     <row r="203">
@@ -3007,7 +3337,7 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>423</v>
+        <v>478</v>
       </c>
     </row>
     <row r="204">
@@ -3015,7 +3345,7 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>424</v>
+        <v>479</v>
       </c>
     </row>
     <row r="205">
@@ -3023,7 +3353,7 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>425</v>
+        <v>480</v>
       </c>
     </row>
     <row r="206">
@@ -3031,7 +3361,7 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>426</v>
+        <v>481</v>
       </c>
     </row>
     <row r="207">
@@ -3039,7 +3369,7 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>427</v>
+        <v>482</v>
       </c>
     </row>
     <row r="208">
@@ -3047,7 +3377,7 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>428</v>
+        <v>483</v>
       </c>
     </row>
     <row r="209">
@@ -3055,7 +3385,7 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>429</v>
+        <v>484</v>
       </c>
     </row>
     <row r="210">
@@ -3063,7 +3393,7 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>430</v>
+        <v>485</v>
       </c>
     </row>
     <row r="211">
@@ -3071,7 +3401,7 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>431</v>
+        <v>486</v>
       </c>
     </row>
     <row r="212">
@@ -3079,7 +3409,7 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>432</v>
+        <v>487</v>
       </c>
     </row>
     <row r="213">
@@ -3087,7 +3417,7 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>433</v>
+        <v>488</v>
       </c>
     </row>
     <row r="214">
@@ -3095,7 +3425,7 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>434</v>
+        <v>489</v>
       </c>
     </row>
     <row r="215">
@@ -3103,7 +3433,7 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>435</v>
+        <v>490</v>
       </c>
     </row>
     <row r="216">
@@ -3111,7 +3441,7 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>436</v>
+        <v>491</v>
       </c>
     </row>
     <row r="217">
@@ -3119,7 +3449,7 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>437</v>
+        <v>492</v>
       </c>
     </row>
     <row r="218">
@@ -3127,7 +3457,7 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>438</v>
+        <v>493</v>
       </c>
     </row>
     <row r="219">
@@ -3135,7 +3465,7 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>439</v>
+        <v>494</v>
       </c>
     </row>
     <row r="220">
@@ -3143,7 +3473,7 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>440</v>
+        <v>495</v>
       </c>
     </row>
     <row r="221">
@@ -3151,7 +3481,7 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>441</v>
+        <v>496</v>
       </c>
     </row>
     <row r="222">
@@ -3159,7 +3489,447 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>442</v>
+        <v>497</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s">
+        <v>222</v>
+      </c>
+      <c r="B223" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s">
+        <v>223</v>
+      </c>
+      <c r="B224" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s">
+        <v>224</v>
+      </c>
+      <c r="B225" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s">
+        <v>225</v>
+      </c>
+      <c r="B226" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s">
+        <v>226</v>
+      </c>
+      <c r="B227" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s">
+        <v>227</v>
+      </c>
+      <c r="B228" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s">
+        <v>228</v>
+      </c>
+      <c r="B229" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s">
+        <v>229</v>
+      </c>
+      <c r="B230" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s">
+        <v>230</v>
+      </c>
+      <c r="B231" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s">
+        <v>231</v>
+      </c>
+      <c r="B232" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s">
+        <v>232</v>
+      </c>
+      <c r="B233" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s">
+        <v>233</v>
+      </c>
+      <c r="B234" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="s">
+        <v>234</v>
+      </c>
+      <c r="B235" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s">
+        <v>235</v>
+      </c>
+      <c r="B236" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s">
+        <v>236</v>
+      </c>
+      <c r="B237" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="s">
+        <v>237</v>
+      </c>
+      <c r="B238" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="s">
+        <v>238</v>
+      </c>
+      <c r="B239" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="s">
+        <v>239</v>
+      </c>
+      <c r="B240" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="s">
+        <v>240</v>
+      </c>
+      <c r="B241" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s">
+        <v>241</v>
+      </c>
+      <c r="B242" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s">
+        <v>242</v>
+      </c>
+      <c r="B243" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s">
+        <v>243</v>
+      </c>
+      <c r="B244" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s">
+        <v>244</v>
+      </c>
+      <c r="B245" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s">
+        <v>245</v>
+      </c>
+      <c r="B246" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s">
+        <v>246</v>
+      </c>
+      <c r="B247" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s">
+        <v>247</v>
+      </c>
+      <c r="B248" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s">
+        <v>248</v>
+      </c>
+      <c r="B249" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s">
+        <v>249</v>
+      </c>
+      <c r="B250" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="s">
+        <v>250</v>
+      </c>
+      <c r="B251" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s">
+        <v>251</v>
+      </c>
+      <c r="B252" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s">
+        <v>252</v>
+      </c>
+      <c r="B253" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s">
+        <v>253</v>
+      </c>
+      <c r="B254" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="s">
+        <v>254</v>
+      </c>
+      <c r="B255" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s">
+        <v>255</v>
+      </c>
+      <c r="B256" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="s">
+        <v>256</v>
+      </c>
+      <c r="B257" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="s">
+        <v>257</v>
+      </c>
+      <c r="B258" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="s">
+        <v>258</v>
+      </c>
+      <c r="B259" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s">
+        <v>259</v>
+      </c>
+      <c r="B260" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s">
+        <v>260</v>
+      </c>
+      <c r="B261" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s">
+        <v>261</v>
+      </c>
+      <c r="B262" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="s">
+        <v>262</v>
+      </c>
+      <c r="B263" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s">
+        <v>263</v>
+      </c>
+      <c r="B264" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s">
+        <v>264</v>
+      </c>
+      <c r="B265" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s">
+        <v>265</v>
+      </c>
+      <c r="B266" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s">
+        <v>266</v>
+      </c>
+      <c r="B267" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s">
+        <v>267</v>
+      </c>
+      <c r="B268" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s">
+        <v>268</v>
+      </c>
+      <c r="B269" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s">
+        <v>269</v>
+      </c>
+      <c r="B270" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s">
+        <v>270</v>
+      </c>
+      <c r="B271" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="s">
+        <v>271</v>
+      </c>
+      <c r="B272" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="s">
+        <v>272</v>
+      </c>
+      <c r="B273" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="s">
+        <v>273</v>
+      </c>
+      <c r="B274" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s">
+        <v>274</v>
+      </c>
+      <c r="B275" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s">
+        <v>275</v>
+      </c>
+      <c r="B276" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s">
+        <v>276</v>
+      </c>
+      <c r="B277" t="s">
+        <v>552</v>
       </c>
     </row>
   </sheetData>

--- a/b1_urls.xlsx
+++ b/b1_urls.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="631">
   <si>
     <t>x</t>
   </si>
@@ -845,6 +845,123 @@
     <t>276</t>
   </si>
   <si>
+    <t>277</t>
+  </si>
+  <si>
+    <t>278</t>
+  </si>
+  <si>
+    <t>279</t>
+  </si>
+  <si>
+    <t>280</t>
+  </si>
+  <si>
+    <t>281</t>
+  </si>
+  <si>
+    <t>282</t>
+  </si>
+  <si>
+    <t>283</t>
+  </si>
+  <si>
+    <t>284</t>
+  </si>
+  <si>
+    <t>285</t>
+  </si>
+  <si>
+    <t>286</t>
+  </si>
+  <si>
+    <t>287</t>
+  </si>
+  <si>
+    <t>288</t>
+  </si>
+  <si>
+    <t>289</t>
+  </si>
+  <si>
+    <t>290</t>
+  </si>
+  <si>
+    <t>291</t>
+  </si>
+  <si>
+    <t>292</t>
+  </si>
+  <si>
+    <t>293</t>
+  </si>
+  <si>
+    <t>294</t>
+  </si>
+  <si>
+    <t>295</t>
+  </si>
+  <si>
+    <t>296</t>
+  </si>
+  <si>
+    <t>297</t>
+  </si>
+  <si>
+    <t>298</t>
+  </si>
+  <si>
+    <t>299</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>301</t>
+  </si>
+  <si>
+    <t>302</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>308</t>
+  </si>
+  <si>
+    <t>309</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>313</t>
+  </si>
+  <si>
+    <t>314</t>
+  </si>
+  <si>
+    <t>315</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/059136bc/Club-Brugge-Mechelen-July-26-2024-Belgian-Pro-League</t>
   </si>
   <si>
@@ -1217,12 +1334,12 @@
     <t>https://fbref.com/en/matches/847465bd/Sint-Truiden-Genk-December-1-2024-Belgian-Pro-League</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/4285d88e/Beerschot-Wilrijk-Cercle-Brugge-December-1-2024-Belgian-Pro-League</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/f9e7c99b/OH-Leuven-Anderlecht-December-1-2024-Belgian-Pro-League</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/4285d88e/Beerschot-Wilrijk-Cercle-Brugge-December-1-2024-Belgian-Pro-League</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/646bb22c/Union-SG-Antwerp-December-1-2024-Belgian-Pro-League</t>
   </si>
   <si>
@@ -1232,12 +1349,12 @@
     <t>https://fbref.com/en/matches/d0dbd9bc/Genk-Kortrijk-December-7-2024-Belgian-Pro-League</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/d4f6d325/Mechelen-Club-Brugge-December-7-2024-Belgian-Pro-League</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/2c12b758/Standard-Liege-OH-Leuven-December-7-2024-Belgian-Pro-League</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/d4f6d325/Mechelen-Club-Brugge-December-7-2024-Belgian-Pro-League</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/3f5bb0d2/Gent-Sint-Truiden-December-7-2024-Belgian-Pro-League</t>
   </si>
   <si>
@@ -1319,12 +1436,12 @@
     <t>https://fbref.com/en/matches/0c9e22f9/OH-Leuven-Beerschot-Wilrijk-December-27-2024-Belgian-Pro-League</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/1fa133d4/Anderlecht-Dender-December-27-2024-Belgian-Pro-League</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/f5c8e1ed/Sint-Truiden-Cercle-Brugge-December-27-2024-Belgian-Pro-League</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/1fa133d4/Anderlecht-Dender-December-27-2024-Belgian-Pro-League</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/3b86978a/Standard-Liege-Kortrijk-January-10-2025-Belgian-Pro-League</t>
   </si>
   <si>
@@ -1550,21 +1667,21 @@
     <t>https://fbref.com/en/matches/3aa7907d/Beerschot-Wilrijk-Westerlo-March-16-2025-Belgian-Pro-League</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/4191f845/OH-Leuven-Sint-Truiden-March-16-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ce003b8c/Anderlecht-Cercle-Brugge-March-16-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8ea772b0/Club-Brugge-Charleroi-March-16-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/f1a378be/Mechelen-Dender-March-16-2025-Belgian-Pro-League</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/02aec0c9/Gent-Kortrijk-March-16-2025-Belgian-Pro-League</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/8ea772b0/Club-Brugge-Charleroi-March-16-2025-Belgian-Pro-League</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/ce003b8c/Anderlecht-Cercle-Brugge-March-16-2025-Belgian-Pro-League</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/4191f845/OH-Leuven-Sint-Truiden-March-16-2025-Belgian-Pro-League</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/ddc2b85a/OH-Leuven-Charleroi-March-28-2025-Belgian-Pro-League</t>
   </si>
   <si>
@@ -1671,6 +1788,123 @@
   </si>
   <si>
     <t>https://fbref.com/en/matches/2dae3b35/Club-Brugge-Union-SG-April-24-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a3c367f6/Beerschot-Wilrijk-Kortrijk-April-25-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d3a2e028/OH-Leuven-Standard-Liege-April-26-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/dc9da5af/Westerlo-Mechelen-April-26-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d4a2d8ec/Cercle-Brugge-Sint-Truiden-April-26-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/dbe09e3f/Charleroi-Dender-April-26-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/06119187/Gent-Anderlecht-April-27-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/5e117f5d/Genk-Antwerp-April-27-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/5b13e6fe/Union-SG-Club-Brugge-April-27-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a0ee8033/Antwerp-Anderlecht-May-1-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/aca4216b/Club-Brugge-Gent-May-1-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/98635ba0/Westerlo-Dender-May-2-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c176ee87/Cercle-Brugge-Kortrijk-May-3-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/dd5e01f6/OH-Leuven-Mechelen-May-3-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/77dd2019/Union-SG-Genk-May-3-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b887e864/Standard-Liege-Charleroi-May-4-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9bbfada1/Sint-Truiden-Beerschot-Wilrijk-May-4-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/07873d2d/Charleroi-Westerlo-May-9-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/789d8512/Kortrijk-Sint-Truiden-May-10-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8242fb6b/Beerschot-Wilrijk-Cercle-Brugge-May-10-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d959ace3/Mechelen-Standard-Liege-May-10-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/af38b7cc/Anderlecht-Union-SG-May-10-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/bf4f0487/Gent-Antwerp-May-11-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/453240e2/Genk-Club-Brugge-May-11-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/6a9c6d0b/Dender-OH-Leuven-May-11-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/0a3b2fb9/OH-Leuven-Westerlo-May-16-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b1dab13e/Standard-Liege-Dender-May-17-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9bcdc718/Antwerp-Union-SG-May-17-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/bd086d64/Anderlecht-Club-Brugge-May-18-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e2e90e7b/Mechelen-Charleroi-May-18-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/47a26f31/Gent-Genk-May-18-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9178eef5/Patro-Eisden-Cercle-Brugge-May-18-2025-Belgian-12-RelegationPromotion-play-offs</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/6c39a34a/Cercle-Brugge-Patro-Eisden-May-23-2025-Belgian-12-RelegationPromotion-play-offs</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/698a42cc/Dender-Mechelen-May-24-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/54a258e4/Westerlo-Standard-Liege-May-24-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/39afee3d/Charleroi-OH-Leuven-May-24-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/95367b2f/Union-SG-Gent-May-25-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/700bb42c/Genk-Anderlecht-May-25-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/609f0e56/Club-Brugge-Antwerp-May-25-2025-Belgian-Pro-League</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/15960bdd/Antwerp-Charleroi-May-29-2025-Belgian-Pro-League</t>
   </si>
 </sst>
 </file>
@@ -1729,7 +1963,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>277</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3">
@@ -1737,7 +1971,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>278</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4">
@@ -1745,7 +1979,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>279</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5">
@@ -1753,7 +1987,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>280</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6">
@@ -1761,7 +1995,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>281</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7">
@@ -1769,7 +2003,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>282</v>
+        <v>321</v>
       </c>
     </row>
     <row r="8">
@@ -1777,7 +2011,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>283</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9">
@@ -1785,7 +2019,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>284</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10">
@@ -1793,7 +2027,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>285</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -1801,7 +2035,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>286</v>
+        <v>325</v>
       </c>
     </row>
     <row r="12">
@@ -1809,7 +2043,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>287</v>
+        <v>326</v>
       </c>
     </row>
     <row r="13">
@@ -1817,7 +2051,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>288</v>
+        <v>327</v>
       </c>
     </row>
     <row r="14">
@@ -1825,7 +2059,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>289</v>
+        <v>328</v>
       </c>
     </row>
     <row r="15">
@@ -1833,7 +2067,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>290</v>
+        <v>329</v>
       </c>
     </row>
     <row r="16">
@@ -1841,7 +2075,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>291</v>
+        <v>330</v>
       </c>
     </row>
     <row r="17">
@@ -1849,7 +2083,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>292</v>
+        <v>331</v>
       </c>
     </row>
     <row r="18">
@@ -1857,7 +2091,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>293</v>
+        <v>332</v>
       </c>
     </row>
     <row r="19">
@@ -1865,7 +2099,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>294</v>
+        <v>333</v>
       </c>
     </row>
     <row r="20">
@@ -1873,7 +2107,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>295</v>
+        <v>334</v>
       </c>
     </row>
     <row r="21">
@@ -1881,7 +2115,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>296</v>
+        <v>335</v>
       </c>
     </row>
     <row r="22">
@@ -1889,7 +2123,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>297</v>
+        <v>336</v>
       </c>
     </row>
     <row r="23">
@@ -1897,7 +2131,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>298</v>
+        <v>337</v>
       </c>
     </row>
     <row r="24">
@@ -1905,7 +2139,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>299</v>
+        <v>338</v>
       </c>
     </row>
     <row r="25">
@@ -1913,7 +2147,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>300</v>
+        <v>339</v>
       </c>
     </row>
     <row r="26">
@@ -1921,7 +2155,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>301</v>
+        <v>340</v>
       </c>
     </row>
     <row r="27">
@@ -1929,7 +2163,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>302</v>
+        <v>341</v>
       </c>
     </row>
     <row r="28">
@@ -1937,7 +2171,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>303</v>
+        <v>342</v>
       </c>
     </row>
     <row r="29">
@@ -1945,7 +2179,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>304</v>
+        <v>343</v>
       </c>
     </row>
     <row r="30">
@@ -1953,7 +2187,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>305</v>
+        <v>344</v>
       </c>
     </row>
     <row r="31">
@@ -1961,7 +2195,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>306</v>
+        <v>345</v>
       </c>
     </row>
     <row r="32">
@@ -1969,7 +2203,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>307</v>
+        <v>346</v>
       </c>
     </row>
     <row r="33">
@@ -1977,7 +2211,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>308</v>
+        <v>347</v>
       </c>
     </row>
     <row r="34">
@@ -1985,7 +2219,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>309</v>
+        <v>348</v>
       </c>
     </row>
     <row r="35">
@@ -1993,7 +2227,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>310</v>
+        <v>349</v>
       </c>
     </row>
     <row r="36">
@@ -2001,7 +2235,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>311</v>
+        <v>350</v>
       </c>
     </row>
     <row r="37">
@@ -2009,7 +2243,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>312</v>
+        <v>351</v>
       </c>
     </row>
     <row r="38">
@@ -2017,7 +2251,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>313</v>
+        <v>352</v>
       </c>
     </row>
     <row r="39">
@@ -2025,7 +2259,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>314</v>
+        <v>353</v>
       </c>
     </row>
     <row r="40">
@@ -2033,7 +2267,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>315</v>
+        <v>354</v>
       </c>
     </row>
     <row r="41">
@@ -2041,7 +2275,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>316</v>
+        <v>355</v>
       </c>
     </row>
     <row r="42">
@@ -2049,7 +2283,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>317</v>
+        <v>356</v>
       </c>
     </row>
     <row r="43">
@@ -2057,7 +2291,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>318</v>
+        <v>357</v>
       </c>
     </row>
     <row r="44">
@@ -2065,7 +2299,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
     </row>
     <row r="45">
@@ -2073,7 +2307,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
     </row>
     <row r="46">
@@ -2081,7 +2315,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>321</v>
+        <v>360</v>
       </c>
     </row>
     <row r="47">
@@ -2089,7 +2323,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>322</v>
+        <v>361</v>
       </c>
     </row>
     <row r="48">
@@ -2097,7 +2331,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>323</v>
+        <v>362</v>
       </c>
     </row>
     <row r="49">
@@ -2105,7 +2339,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>324</v>
+        <v>363</v>
       </c>
     </row>
     <row r="50">
@@ -2113,7 +2347,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>325</v>
+        <v>364</v>
       </c>
     </row>
     <row r="51">
@@ -2121,7 +2355,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>326</v>
+        <v>365</v>
       </c>
     </row>
     <row r="52">
@@ -2129,7 +2363,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>327</v>
+        <v>366</v>
       </c>
     </row>
     <row r="53">
@@ -2137,7 +2371,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>328</v>
+        <v>367</v>
       </c>
     </row>
     <row r="54">
@@ -2145,7 +2379,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>329</v>
+        <v>368</v>
       </c>
     </row>
     <row r="55">
@@ -2153,7 +2387,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>330</v>
+        <v>369</v>
       </c>
     </row>
     <row r="56">
@@ -2161,7 +2395,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>331</v>
+        <v>370</v>
       </c>
     </row>
     <row r="57">
@@ -2169,7 +2403,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>332</v>
+        <v>371</v>
       </c>
     </row>
     <row r="58">
@@ -2177,7 +2411,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>333</v>
+        <v>372</v>
       </c>
     </row>
     <row r="59">
@@ -2185,7 +2419,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>334</v>
+        <v>373</v>
       </c>
     </row>
     <row r="60">
@@ -2193,7 +2427,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
     </row>
     <row r="61">
@@ -2201,7 +2435,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>336</v>
+        <v>375</v>
       </c>
     </row>
     <row r="62">
@@ -2209,7 +2443,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>337</v>
+        <v>376</v>
       </c>
     </row>
     <row r="63">
@@ -2217,7 +2451,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>338</v>
+        <v>377</v>
       </c>
     </row>
     <row r="64">
@@ -2225,7 +2459,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>339</v>
+        <v>378</v>
       </c>
     </row>
     <row r="65">
@@ -2233,7 +2467,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>340</v>
+        <v>379</v>
       </c>
     </row>
     <row r="66">
@@ -2241,7 +2475,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>341</v>
+        <v>380</v>
       </c>
     </row>
     <row r="67">
@@ -2249,7 +2483,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>342</v>
+        <v>381</v>
       </c>
     </row>
     <row r="68">
@@ -2257,7 +2491,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>343</v>
+        <v>382</v>
       </c>
     </row>
     <row r="69">
@@ -2265,7 +2499,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>344</v>
+        <v>383</v>
       </c>
     </row>
     <row r="70">
@@ -2273,7 +2507,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>345</v>
+        <v>384</v>
       </c>
     </row>
     <row r="71">
@@ -2281,7 +2515,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>346</v>
+        <v>385</v>
       </c>
     </row>
     <row r="72">
@@ -2289,7 +2523,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>347</v>
+        <v>386</v>
       </c>
     </row>
     <row r="73">
@@ -2297,7 +2531,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>348</v>
+        <v>387</v>
       </c>
     </row>
     <row r="74">
@@ -2305,7 +2539,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>349</v>
+        <v>388</v>
       </c>
     </row>
     <row r="75">
@@ -2313,7 +2547,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>350</v>
+        <v>389</v>
       </c>
     </row>
     <row r="76">
@@ -2321,7 +2555,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>351</v>
+        <v>390</v>
       </c>
     </row>
     <row r="77">
@@ -2329,7 +2563,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="78">
@@ -2337,7 +2571,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>353</v>
+        <v>392</v>
       </c>
     </row>
     <row r="79">
@@ -2345,7 +2579,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>354</v>
+        <v>393</v>
       </c>
     </row>
     <row r="80">
@@ -2353,7 +2587,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>355</v>
+        <v>394</v>
       </c>
     </row>
     <row r="81">
@@ -2361,7 +2595,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>356</v>
+        <v>395</v>
       </c>
     </row>
     <row r="82">
@@ -2369,7 +2603,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>357</v>
+        <v>396</v>
       </c>
     </row>
     <row r="83">
@@ -2377,7 +2611,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>358</v>
+        <v>397</v>
       </c>
     </row>
     <row r="84">
@@ -2385,7 +2619,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>359</v>
+        <v>398</v>
       </c>
     </row>
     <row r="85">
@@ -2393,7 +2627,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>360</v>
+        <v>399</v>
       </c>
     </row>
     <row r="86">
@@ -2401,7 +2635,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>361</v>
+        <v>400</v>
       </c>
     </row>
     <row r="87">
@@ -2409,7 +2643,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>362</v>
+        <v>401</v>
       </c>
     </row>
     <row r="88">
@@ -2417,7 +2651,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>363</v>
+        <v>402</v>
       </c>
     </row>
     <row r="89">
@@ -2425,7 +2659,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>364</v>
+        <v>403</v>
       </c>
     </row>
     <row r="90">
@@ -2433,7 +2667,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>365</v>
+        <v>404</v>
       </c>
     </row>
     <row r="91">
@@ -2441,7 +2675,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>366</v>
+        <v>405</v>
       </c>
     </row>
     <row r="92">
@@ -2449,7 +2683,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>367</v>
+        <v>406</v>
       </c>
     </row>
     <row r="93">
@@ -2457,7 +2691,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>368</v>
+        <v>407</v>
       </c>
     </row>
     <row r="94">
@@ -2465,7 +2699,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>369</v>
+        <v>408</v>
       </c>
     </row>
     <row r="95">
@@ -2473,7 +2707,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>370</v>
+        <v>409</v>
       </c>
     </row>
     <row r="96">
@@ -2481,7 +2715,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>371</v>
+        <v>410</v>
       </c>
     </row>
     <row r="97">
@@ -2489,7 +2723,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>372</v>
+        <v>411</v>
       </c>
     </row>
     <row r="98">
@@ -2497,7 +2731,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>373</v>
+        <v>412</v>
       </c>
     </row>
     <row r="99">
@@ -2505,7 +2739,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>374</v>
+        <v>413</v>
       </c>
     </row>
     <row r="100">
@@ -2513,7 +2747,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>375</v>
+        <v>414</v>
       </c>
     </row>
     <row r="101">
@@ -2521,7 +2755,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>376</v>
+        <v>415</v>
       </c>
     </row>
     <row r="102">
@@ -2529,7 +2763,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>377</v>
+        <v>416</v>
       </c>
     </row>
     <row r="103">
@@ -2537,7 +2771,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>378</v>
+        <v>417</v>
       </c>
     </row>
     <row r="104">
@@ -2545,7 +2779,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>379</v>
+        <v>418</v>
       </c>
     </row>
     <row r="105">
@@ -2553,7 +2787,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>380</v>
+        <v>419</v>
       </c>
     </row>
     <row r="106">
@@ -2561,7 +2795,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>381</v>
+        <v>420</v>
       </c>
     </row>
     <row r="107">
@@ -2569,7 +2803,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>382</v>
+        <v>421</v>
       </c>
     </row>
     <row r="108">
@@ -2577,7 +2811,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>383</v>
+        <v>422</v>
       </c>
     </row>
     <row r="109">
@@ -2585,7 +2819,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>384</v>
+        <v>423</v>
       </c>
     </row>
     <row r="110">
@@ -2593,7 +2827,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>385</v>
+        <v>424</v>
       </c>
     </row>
     <row r="111">
@@ -2601,7 +2835,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>386</v>
+        <v>425</v>
       </c>
     </row>
     <row r="112">
@@ -2609,7 +2843,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>387</v>
+        <v>426</v>
       </c>
     </row>
     <row r="113">
@@ -2617,7 +2851,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>388</v>
+        <v>427</v>
       </c>
     </row>
     <row r="114">
@@ -2625,7 +2859,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
     </row>
     <row r="115">
@@ -2633,7 +2867,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>390</v>
+        <v>429</v>
       </c>
     </row>
     <row r="116">
@@ -2641,7 +2875,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>391</v>
+        <v>430</v>
       </c>
     </row>
     <row r="117">
@@ -2649,7 +2883,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>392</v>
+        <v>431</v>
       </c>
     </row>
     <row r="118">
@@ -2657,7 +2891,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>393</v>
+        <v>432</v>
       </c>
     </row>
     <row r="119">
@@ -2665,7 +2899,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>394</v>
+        <v>433</v>
       </c>
     </row>
     <row r="120">
@@ -2673,7 +2907,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>395</v>
+        <v>434</v>
       </c>
     </row>
     <row r="121">
@@ -2681,7 +2915,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>396</v>
+        <v>435</v>
       </c>
     </row>
     <row r="122">
@@ -2689,7 +2923,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>397</v>
+        <v>436</v>
       </c>
     </row>
     <row r="123">
@@ -2697,7 +2931,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>398</v>
+        <v>437</v>
       </c>
     </row>
     <row r="124">
@@ -2705,7 +2939,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>399</v>
+        <v>438</v>
       </c>
     </row>
     <row r="125">
@@ -2713,7 +2947,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>400</v>
+        <v>439</v>
       </c>
     </row>
     <row r="126">
@@ -2721,7 +2955,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>401</v>
+        <v>440</v>
       </c>
     </row>
     <row r="127">
@@ -2729,7 +2963,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>402</v>
+        <v>441</v>
       </c>
     </row>
     <row r="128">
@@ -2737,7 +2971,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>403</v>
+        <v>442</v>
       </c>
     </row>
     <row r="129">
@@ -2745,7 +2979,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>404</v>
+        <v>443</v>
       </c>
     </row>
     <row r="130">
@@ -2753,7 +2987,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>405</v>
+        <v>444</v>
       </c>
     </row>
     <row r="131">
@@ -2761,7 +2995,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>406</v>
+        <v>445</v>
       </c>
     </row>
     <row r="132">
@@ -2769,7 +3003,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
     </row>
     <row r="133">
@@ -2777,7 +3011,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
     </row>
     <row r="134">
@@ -2785,7 +3019,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>409</v>
+        <v>448</v>
       </c>
     </row>
     <row r="135">
@@ -2793,7 +3027,7 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>410</v>
+        <v>449</v>
       </c>
     </row>
     <row r="136">
@@ -2801,7 +3035,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>411</v>
+        <v>450</v>
       </c>
     </row>
     <row r="137">
@@ -2809,7 +3043,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>412</v>
+        <v>451</v>
       </c>
     </row>
     <row r="138">
@@ -2817,7 +3051,7 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="139">
@@ -2825,7 +3059,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>414</v>
+        <v>453</v>
       </c>
     </row>
     <row r="140">
@@ -2833,7 +3067,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>415</v>
+        <v>454</v>
       </c>
     </row>
     <row r="141">
@@ -2841,7 +3075,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>416</v>
+        <v>455</v>
       </c>
     </row>
     <row r="142">
@@ -2849,7 +3083,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>417</v>
+        <v>456</v>
       </c>
     </row>
     <row r="143">
@@ -2857,7 +3091,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>418</v>
+        <v>457</v>
       </c>
     </row>
     <row r="144">
@@ -2865,7 +3099,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>419</v>
+        <v>458</v>
       </c>
     </row>
     <row r="145">
@@ -2873,7 +3107,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>420</v>
+        <v>459</v>
       </c>
     </row>
     <row r="146">
@@ -2881,7 +3115,7 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>421</v>
+        <v>460</v>
       </c>
     </row>
     <row r="147">
@@ -2889,7 +3123,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>422</v>
+        <v>461</v>
       </c>
     </row>
     <row r="148">
@@ -2897,7 +3131,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>423</v>
+        <v>462</v>
       </c>
     </row>
     <row r="149">
@@ -2905,7 +3139,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>424</v>
+        <v>463</v>
       </c>
     </row>
     <row r="150">
@@ -2913,7 +3147,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>425</v>
+        <v>464</v>
       </c>
     </row>
     <row r="151">
@@ -2921,7 +3155,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>426</v>
+        <v>465</v>
       </c>
     </row>
     <row r="152">
@@ -2929,7 +3163,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>427</v>
+        <v>466</v>
       </c>
     </row>
     <row r="153">
@@ -2937,7 +3171,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>428</v>
+        <v>467</v>
       </c>
     </row>
     <row r="154">
@@ -2945,7 +3179,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>429</v>
+        <v>468</v>
       </c>
     </row>
     <row r="155">
@@ -2953,7 +3187,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>430</v>
+        <v>469</v>
       </c>
     </row>
     <row r="156">
@@ -2961,7 +3195,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>431</v>
+        <v>470</v>
       </c>
     </row>
     <row r="157">
@@ -2969,7 +3203,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>432</v>
+        <v>471</v>
       </c>
     </row>
     <row r="158">
@@ -2977,7 +3211,7 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>433</v>
+        <v>472</v>
       </c>
     </row>
     <row r="159">
@@ -2985,7 +3219,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>434</v>
+        <v>473</v>
       </c>
     </row>
     <row r="160">
@@ -2993,7 +3227,7 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>435</v>
+        <v>474</v>
       </c>
     </row>
     <row r="161">
@@ -3001,7 +3235,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>436</v>
+        <v>475</v>
       </c>
     </row>
     <row r="162">
@@ -3009,7 +3243,7 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>437</v>
+        <v>476</v>
       </c>
     </row>
     <row r="163">
@@ -3017,7 +3251,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>438</v>
+        <v>477</v>
       </c>
     </row>
     <row r="164">
@@ -3025,7 +3259,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>439</v>
+        <v>478</v>
       </c>
     </row>
     <row r="165">
@@ -3033,7 +3267,7 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>440</v>
+        <v>479</v>
       </c>
     </row>
     <row r="166">
@@ -3041,7 +3275,7 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>441</v>
+        <v>480</v>
       </c>
     </row>
     <row r="167">
@@ -3049,7 +3283,7 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>442</v>
+        <v>481</v>
       </c>
     </row>
     <row r="168">
@@ -3057,7 +3291,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>443</v>
+        <v>482</v>
       </c>
     </row>
     <row r="169">
@@ -3065,7 +3299,7 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>444</v>
+        <v>483</v>
       </c>
     </row>
     <row r="170">
@@ -3073,7 +3307,7 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>445</v>
+        <v>484</v>
       </c>
     </row>
     <row r="171">
@@ -3081,7 +3315,7 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>446</v>
+        <v>485</v>
       </c>
     </row>
     <row r="172">
@@ -3089,7 +3323,7 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>447</v>
+        <v>486</v>
       </c>
     </row>
     <row r="173">
@@ -3097,7 +3331,7 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>448</v>
+        <v>487</v>
       </c>
     </row>
     <row r="174">
@@ -3105,7 +3339,7 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>449</v>
+        <v>488</v>
       </c>
     </row>
     <row r="175">
@@ -3113,7 +3347,7 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>450</v>
+        <v>489</v>
       </c>
     </row>
     <row r="176">
@@ -3121,7 +3355,7 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>451</v>
+        <v>490</v>
       </c>
     </row>
     <row r="177">
@@ -3129,7 +3363,7 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>452</v>
+        <v>491</v>
       </c>
     </row>
     <row r="178">
@@ -3137,7 +3371,7 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>453</v>
+        <v>492</v>
       </c>
     </row>
     <row r="179">
@@ -3145,7 +3379,7 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>454</v>
+        <v>493</v>
       </c>
     </row>
     <row r="180">
@@ -3153,7 +3387,7 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>455</v>
+        <v>494</v>
       </c>
     </row>
     <row r="181">
@@ -3161,7 +3395,7 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>456</v>
+        <v>495</v>
       </c>
     </row>
     <row r="182">
@@ -3169,7 +3403,7 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>457</v>
+        <v>496</v>
       </c>
     </row>
     <row r="183">
@@ -3177,7 +3411,7 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>458</v>
+        <v>497</v>
       </c>
     </row>
     <row r="184">
@@ -3185,7 +3419,7 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="185">
@@ -3193,7 +3427,7 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>460</v>
+        <v>499</v>
       </c>
     </row>
     <row r="186">
@@ -3201,7 +3435,7 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>461</v>
+        <v>500</v>
       </c>
     </row>
     <row r="187">
@@ -3209,7 +3443,7 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>462</v>
+        <v>501</v>
       </c>
     </row>
     <row r="188">
@@ -3217,7 +3451,7 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>463</v>
+        <v>502</v>
       </c>
     </row>
     <row r="189">
@@ -3225,7 +3459,7 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>464</v>
+        <v>503</v>
       </c>
     </row>
     <row r="190">
@@ -3233,7 +3467,7 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>465</v>
+        <v>504</v>
       </c>
     </row>
     <row r="191">
@@ -3241,7 +3475,7 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>466</v>
+        <v>505</v>
       </c>
     </row>
     <row r="192">
@@ -3249,7 +3483,7 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>467</v>
+        <v>506</v>
       </c>
     </row>
     <row r="193">
@@ -3257,7 +3491,7 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>468</v>
+        <v>507</v>
       </c>
     </row>
     <row r="194">
@@ -3265,7 +3499,7 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>469</v>
+        <v>508</v>
       </c>
     </row>
     <row r="195">
@@ -3273,7 +3507,7 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>470</v>
+        <v>509</v>
       </c>
     </row>
     <row r="196">
@@ -3281,7 +3515,7 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>471</v>
+        <v>510</v>
       </c>
     </row>
     <row r="197">
@@ -3289,7 +3523,7 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>472</v>
+        <v>511</v>
       </c>
     </row>
     <row r="198">
@@ -3297,7 +3531,7 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>473</v>
+        <v>512</v>
       </c>
     </row>
     <row r="199">
@@ -3305,7 +3539,7 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>474</v>
+        <v>513</v>
       </c>
     </row>
     <row r="200">
@@ -3313,7 +3547,7 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>475</v>
+        <v>514</v>
       </c>
     </row>
     <row r="201">
@@ -3321,7 +3555,7 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
     </row>
     <row r="202">
@@ -3329,7 +3563,7 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>477</v>
+        <v>516</v>
       </c>
     </row>
     <row r="203">
@@ -3337,7 +3571,7 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>478</v>
+        <v>517</v>
       </c>
     </row>
     <row r="204">
@@ -3345,7 +3579,7 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>479</v>
+        <v>518</v>
       </c>
     </row>
     <row r="205">
@@ -3353,7 +3587,7 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>480</v>
+        <v>519</v>
       </c>
     </row>
     <row r="206">
@@ -3361,7 +3595,7 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>481</v>
+        <v>520</v>
       </c>
     </row>
     <row r="207">
@@ -3369,7 +3603,7 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>482</v>
+        <v>521</v>
       </c>
     </row>
     <row r="208">
@@ -3377,7 +3611,7 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>483</v>
+        <v>522</v>
       </c>
     </row>
     <row r="209">
@@ -3385,7 +3619,7 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>484</v>
+        <v>523</v>
       </c>
     </row>
     <row r="210">
@@ -3393,7 +3627,7 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>485</v>
+        <v>524</v>
       </c>
     </row>
     <row r="211">
@@ -3401,7 +3635,7 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>486</v>
+        <v>525</v>
       </c>
     </row>
     <row r="212">
@@ -3409,7 +3643,7 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>487</v>
+        <v>526</v>
       </c>
     </row>
     <row r="213">
@@ -3417,7 +3651,7 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>488</v>
+        <v>527</v>
       </c>
     </row>
     <row r="214">
@@ -3425,7 +3659,7 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>489</v>
+        <v>528</v>
       </c>
     </row>
     <row r="215">
@@ -3433,7 +3667,7 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>490</v>
+        <v>529</v>
       </c>
     </row>
     <row r="216">
@@ -3441,7 +3675,7 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>491</v>
+        <v>530</v>
       </c>
     </row>
     <row r="217">
@@ -3449,7 +3683,7 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>492</v>
+        <v>531</v>
       </c>
     </row>
     <row r="218">
@@ -3457,7 +3691,7 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>493</v>
+        <v>532</v>
       </c>
     </row>
     <row r="219">
@@ -3465,7 +3699,7 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>494</v>
+        <v>533</v>
       </c>
     </row>
     <row r="220">
@@ -3473,7 +3707,7 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>495</v>
+        <v>534</v>
       </c>
     </row>
     <row r="221">
@@ -3481,7 +3715,7 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>496</v>
+        <v>535</v>
       </c>
     </row>
     <row r="222">
@@ -3489,7 +3723,7 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>497</v>
+        <v>536</v>
       </c>
     </row>
     <row r="223">
@@ -3497,7 +3731,7 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>498</v>
+        <v>537</v>
       </c>
     </row>
     <row r="224">
@@ -3505,7 +3739,7 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>499</v>
+        <v>538</v>
       </c>
     </row>
     <row r="225">
@@ -3513,7 +3747,7 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>500</v>
+        <v>539</v>
       </c>
     </row>
     <row r="226">
@@ -3521,7 +3755,7 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>501</v>
+        <v>540</v>
       </c>
     </row>
     <row r="227">
@@ -3529,7 +3763,7 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>502</v>
+        <v>541</v>
       </c>
     </row>
     <row r="228">
@@ -3537,7 +3771,7 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>503</v>
+        <v>542</v>
       </c>
     </row>
     <row r="229">
@@ -3545,7 +3779,7 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>504</v>
+        <v>543</v>
       </c>
     </row>
     <row r="230">
@@ -3553,7 +3787,7 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>505</v>
+        <v>544</v>
       </c>
     </row>
     <row r="231">
@@ -3561,7 +3795,7 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>506</v>
+        <v>545</v>
       </c>
     </row>
     <row r="232">
@@ -3569,7 +3803,7 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>507</v>
+        <v>546</v>
       </c>
     </row>
     <row r="233">
@@ -3577,7 +3811,7 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>508</v>
+        <v>547</v>
       </c>
     </row>
     <row r="234">
@@ -3585,7 +3819,7 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>509</v>
+        <v>548</v>
       </c>
     </row>
     <row r="235">
@@ -3593,7 +3827,7 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>510</v>
+        <v>549</v>
       </c>
     </row>
     <row r="236">
@@ -3601,7 +3835,7 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>511</v>
+        <v>550</v>
       </c>
     </row>
     <row r="237">
@@ -3609,7 +3843,7 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>512</v>
+        <v>551</v>
       </c>
     </row>
     <row r="238">
@@ -3617,7 +3851,7 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>513</v>
+        <v>552</v>
       </c>
     </row>
     <row r="239">
@@ -3625,7 +3859,7 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>514</v>
+        <v>553</v>
       </c>
     </row>
     <row r="240">
@@ -3633,7 +3867,7 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>515</v>
+        <v>554</v>
       </c>
     </row>
     <row r="241">
@@ -3641,7 +3875,7 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>516</v>
+        <v>555</v>
       </c>
     </row>
     <row r="242">
@@ -3649,7 +3883,7 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>517</v>
+        <v>556</v>
       </c>
     </row>
     <row r="243">
@@ -3657,7 +3891,7 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>518</v>
+        <v>557</v>
       </c>
     </row>
     <row r="244">
@@ -3665,7 +3899,7 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>519</v>
+        <v>558</v>
       </c>
     </row>
     <row r="245">
@@ -3673,7 +3907,7 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>520</v>
+        <v>559</v>
       </c>
     </row>
     <row r="246">
@@ -3681,7 +3915,7 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>521</v>
+        <v>560</v>
       </c>
     </row>
     <row r="247">
@@ -3689,7 +3923,7 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>522</v>
+        <v>561</v>
       </c>
     </row>
     <row r="248">
@@ -3697,7 +3931,7 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>523</v>
+        <v>562</v>
       </c>
     </row>
     <row r="249">
@@ -3705,7 +3939,7 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>524</v>
+        <v>563</v>
       </c>
     </row>
     <row r="250">
@@ -3713,7 +3947,7 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>525</v>
+        <v>564</v>
       </c>
     </row>
     <row r="251">
@@ -3721,7 +3955,7 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>526</v>
+        <v>565</v>
       </c>
     </row>
     <row r="252">
@@ -3729,7 +3963,7 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>527</v>
+        <v>566</v>
       </c>
     </row>
     <row r="253">
@@ -3737,7 +3971,7 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>528</v>
+        <v>567</v>
       </c>
     </row>
     <row r="254">
@@ -3745,7 +3979,7 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>529</v>
+        <v>568</v>
       </c>
     </row>
     <row r="255">
@@ -3753,7 +3987,7 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>530</v>
+        <v>569</v>
       </c>
     </row>
     <row r="256">
@@ -3761,7 +3995,7 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>531</v>
+        <v>570</v>
       </c>
     </row>
     <row r="257">
@@ -3769,7 +4003,7 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>532</v>
+        <v>571</v>
       </c>
     </row>
     <row r="258">
@@ -3777,7 +4011,7 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>533</v>
+        <v>572</v>
       </c>
     </row>
     <row r="259">
@@ -3785,7 +4019,7 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>534</v>
+        <v>573</v>
       </c>
     </row>
     <row r="260">
@@ -3793,7 +4027,7 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>535</v>
+        <v>574</v>
       </c>
     </row>
     <row r="261">
@@ -3801,7 +4035,7 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>536</v>
+        <v>575</v>
       </c>
     </row>
     <row r="262">
@@ -3809,7 +4043,7 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>537</v>
+        <v>576</v>
       </c>
     </row>
     <row r="263">
@@ -3817,7 +4051,7 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>538</v>
+        <v>577</v>
       </c>
     </row>
     <row r="264">
@@ -3825,7 +4059,7 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>539</v>
+        <v>578</v>
       </c>
     </row>
     <row r="265">
@@ -3833,7 +4067,7 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>540</v>
+        <v>579</v>
       </c>
     </row>
     <row r="266">
@@ -3841,7 +4075,7 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>541</v>
+        <v>580</v>
       </c>
     </row>
     <row r="267">
@@ -3849,7 +4083,7 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>542</v>
+        <v>581</v>
       </c>
     </row>
     <row r="268">
@@ -3857,7 +4091,7 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>543</v>
+        <v>582</v>
       </c>
     </row>
     <row r="269">
@@ -3865,7 +4099,7 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>544</v>
+        <v>583</v>
       </c>
     </row>
     <row r="270">
@@ -3873,7 +4107,7 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>545</v>
+        <v>584</v>
       </c>
     </row>
     <row r="271">
@@ -3881,7 +4115,7 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>546</v>
+        <v>585</v>
       </c>
     </row>
     <row r="272">
@@ -3889,7 +4123,7 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>547</v>
+        <v>586</v>
       </c>
     </row>
     <row r="273">
@@ -3897,7 +4131,7 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>548</v>
+        <v>587</v>
       </c>
     </row>
     <row r="274">
@@ -3905,7 +4139,7 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>549</v>
+        <v>588</v>
       </c>
     </row>
     <row r="275">
@@ -3913,7 +4147,7 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>550</v>
+        <v>589</v>
       </c>
     </row>
     <row r="276">
@@ -3921,7 +4155,7 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>551</v>
+        <v>590</v>
       </c>
     </row>
     <row r="277">
@@ -3929,7 +4163,319 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>552</v>
+        <v>591</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="s">
+        <v>277</v>
+      </c>
+      <c r="B278" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="s">
+        <v>278</v>
+      </c>
+      <c r="B279" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="s">
+        <v>279</v>
+      </c>
+      <c r="B280" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s">
+        <v>280</v>
+      </c>
+      <c r="B281" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s">
+        <v>281</v>
+      </c>
+      <c r="B282" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s">
+        <v>282</v>
+      </c>
+      <c r="B283" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="s">
+        <v>283</v>
+      </c>
+      <c r="B284" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="s">
+        <v>284</v>
+      </c>
+      <c r="B285" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="s">
+        <v>285</v>
+      </c>
+      <c r="B286" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="s">
+        <v>286</v>
+      </c>
+      <c r="B287" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="s">
+        <v>287</v>
+      </c>
+      <c r="B288" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="s">
+        <v>288</v>
+      </c>
+      <c r="B289" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="s">
+        <v>289</v>
+      </c>
+      <c r="B290" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="s">
+        <v>290</v>
+      </c>
+      <c r="B291" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="s">
+        <v>291</v>
+      </c>
+      <c r="B292" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="s">
+        <v>292</v>
+      </c>
+      <c r="B293" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="s">
+        <v>293</v>
+      </c>
+      <c r="B294" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="s">
+        <v>294</v>
+      </c>
+      <c r="B295" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="s">
+        <v>295</v>
+      </c>
+      <c r="B296" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="s">
+        <v>296</v>
+      </c>
+      <c r="B297" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="s">
+        <v>297</v>
+      </c>
+      <c r="B298" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="s">
+        <v>298</v>
+      </c>
+      <c r="B299" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="s">
+        <v>299</v>
+      </c>
+      <c r="B300" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="s">
+        <v>300</v>
+      </c>
+      <c r="B301" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="s">
+        <v>301</v>
+      </c>
+      <c r="B302" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="s">
+        <v>302</v>
+      </c>
+      <c r="B303" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="s">
+        <v>303</v>
+      </c>
+      <c r="B304" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="s">
+        <v>304</v>
+      </c>
+      <c r="B305" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="s">
+        <v>305</v>
+      </c>
+      <c r="B306" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="s">
+        <v>306</v>
+      </c>
+      <c r="B307" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="s">
+        <v>307</v>
+      </c>
+      <c r="B308" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="s">
+        <v>308</v>
+      </c>
+      <c r="B309" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="s">
+        <v>309</v>
+      </c>
+      <c r="B310" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="s">
+        <v>310</v>
+      </c>
+      <c r="B311" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="s">
+        <v>311</v>
+      </c>
+      <c r="B312" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="s">
+        <v>312</v>
+      </c>
+      <c r="B313" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="s">
+        <v>313</v>
+      </c>
+      <c r="B314" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="s">
+        <v>314</v>
+      </c>
+      <c r="B315" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="s">
+        <v>315</v>
+      </c>
+      <c r="B316" t="s">
+        <v>630</v>
       </c>
     </row>
   </sheetData>
